--- a/Build/_Archive_VersionA_LivingIndependently/BUILD_SOW_2026-27_vA_with_LivingIndependently.xlsx
+++ b/Build/_Archive_VersionA_LivingIndependently/BUILD_SOW_2026-27_vA_with_LivingIndependently.xlsx
@@ -8529,7 +8529,7 @@
     <row r="65" ht="19.5" customHeight="1" s="15">
       <c r="A65" s="58" t="inlineStr">
         <is>
-          <t>SUMMER TERM 2  ·  June, end of academic year 2027</t>
+          <t>SUMMER TERM 2  ·  21 July, end of academic year 2027</t>
         </is>
       </c>
       <c r="B65" s="70" t="n"/>
